--- a/labeled/Add_Eating/July/multi_seed_results/seed_123/predictions.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_123/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,242 +442,242 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.926108360290527</v>
+        <v>9.189723014831543</v>
       </c>
       <c r="B2" t="n">
-        <v>11.85279941558838</v>
+        <v>9.478271484375</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10.7737512588501</v>
+        <v>21.5475025177002</v>
       </c>
       <c r="B3" t="n">
-        <v>9.908841133117676</v>
+        <v>18.70711708068848</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20</v>
+        <v>10.47430801391602</v>
       </c>
       <c r="B4" t="n">
-        <v>34.49066162109375</v>
+        <v>15.20250511169434</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8.275861740112305</v>
+        <v>14.18650817871094</v>
       </c>
       <c r="B5" t="n">
-        <v>11.43957138061523</v>
+        <v>15.35685157775879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21.5475025177002</v>
+        <v>6.646825313568115</v>
       </c>
       <c r="B6" t="n">
-        <v>21.37415504455566</v>
+        <v>16.87665939331055</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.938295841217041</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="B7" t="n">
-        <v>9.36646842956543</v>
+        <v>108.3861846923828</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>25.79365158081055</v>
+        <v>13.4285717010498</v>
       </c>
       <c r="B8" t="n">
-        <v>14.36980056762695</v>
+        <v>20.50985527038574</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11.56126499176025</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="B9" t="n">
-        <v>16.47593688964844</v>
+        <v>16.64835548400879</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>28.20763969421387</v>
+        <v>3.428011655807495</v>
       </c>
       <c r="B10" t="n">
-        <v>25.55939865112305</v>
+        <v>11.62607192993164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>23.01665115356445</v>
+        <v>5.221674919128418</v>
       </c>
       <c r="B11" t="n">
-        <v>21.66036224365234</v>
+        <v>6.749958515167236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>25.09920692443848</v>
+        <v>25.75905990600586</v>
       </c>
       <c r="B12" t="n">
-        <v>23.52532577514648</v>
+        <v>23.0378532409668</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20.33730125427246</v>
+        <v>29.10000038146973</v>
       </c>
       <c r="B13" t="n">
-        <v>23.21025085449219</v>
+        <v>30.65419387817383</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18.4761905670166</v>
+        <v>40.25465393066406</v>
       </c>
       <c r="B14" t="n">
-        <v>18.0265007019043</v>
+        <v>44.82844161987305</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12.54940700531006</v>
+        <v>26.28968238830566</v>
       </c>
       <c r="B15" t="n">
-        <v>14.09376430511475</v>
+        <v>23.82186698913574</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>40</v>
+        <v>20.53571510314941</v>
       </c>
       <c r="B16" t="n">
-        <v>59.47654724121094</v>
+        <v>14.69947814941406</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103.8000030517578</v>
+        <v>11.7142858505249</v>
       </c>
       <c r="B17" t="n">
-        <v>97.61961364746094</v>
+        <v>10.04952144622803</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>29.10000038146973</v>
+        <v>24.68168449401855</v>
       </c>
       <c r="B18" t="n">
-        <v>24.70599937438965</v>
+        <v>17.32084274291992</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>39.17727661132812</v>
+        <v>59</v>
       </c>
       <c r="B19" t="n">
-        <v>35.33559799194336</v>
+        <v>45.84957504272461</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19.84127044677734</v>
+        <v>11.2380952835083</v>
       </c>
       <c r="B20" t="n">
-        <v>22.36098480224609</v>
+        <v>10.54683876037598</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80</v>
+        <v>20.73412704467773</v>
       </c>
       <c r="B21" t="n">
-        <v>71.05564880371094</v>
+        <v>26.5905818939209</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>19.5</v>
+        <v>24.38785552978516</v>
       </c>
       <c r="B22" t="n">
-        <v>14.51790237426758</v>
+        <v>29.51544380187988</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>59.70000076293945</v>
+        <v>40.27777862548828</v>
       </c>
       <c r="B23" t="n">
-        <v>62.00216293334961</v>
+        <v>31.6482048034668</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>41.52381134033203</v>
+        <v>15.57539653778076</v>
       </c>
       <c r="B24" t="n">
-        <v>34.33946228027344</v>
+        <v>12.05312538146973</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>54.66666793823242</v>
+        <v>73.40000152587891</v>
       </c>
       <c r="B25" t="n">
-        <v>54.96805191040039</v>
+        <v>79.25946807861328</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>43.79999923706055</v>
+        <v>20.17629814147949</v>
       </c>
       <c r="B26" t="n">
-        <v>39.87178421020508</v>
+        <v>19.300048828125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26.05288887023926</v>
+        <v>12.74703598022461</v>
       </c>
       <c r="B27" t="n">
-        <v>25.30001068115234</v>
+        <v>15.42073249816895</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3.917727708816528</v>
+        <v>17.94871711730957</v>
       </c>
       <c r="B28" t="n">
-        <v>10.53113651275635</v>
+        <v>23.51278305053711</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>60.82272338867188</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B29" t="n">
-        <v>59.26974105834961</v>
+        <v>18.88224601745605</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30.55827713012695</v>
+        <v>5.320197105407715</v>
       </c>
       <c r="B30" t="n">
-        <v>34.38868713378906</v>
+        <v>13.45578765869141</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>39.5</v>
+        <v>5.582761764526367</v>
       </c>
       <c r="B31" t="n">
-        <v>37.15991592407227</v>
+        <v>12.02873992919922</v>
       </c>
     </row>
     <row r="32">
@@ -685,919 +685,503 @@
         <v>19.84127044677734</v>
       </c>
       <c r="B32" t="n">
-        <v>27.16770935058594</v>
+        <v>21.54719543457031</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19.84127044677734</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="B33" t="n">
-        <v>14.84048080444336</v>
+        <v>38.75202941894531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>26.28968238830566</v>
+        <v>13.89999961853027</v>
       </c>
       <c r="B34" t="n">
-        <v>25.08518028259277</v>
+        <v>13.33189105987549</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>73.5</v>
+        <v>2.938295841217041</v>
       </c>
       <c r="B35" t="n">
-        <v>71.70229339599609</v>
+        <v>9.83796215057373</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>40</v>
+        <v>8.952381134033203</v>
       </c>
       <c r="B36" t="n">
-        <v>41.82664489746094</v>
+        <v>15.3159761428833</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>35.29999923706055</v>
+        <v>33.5</v>
       </c>
       <c r="B37" t="n">
-        <v>35.93647384643555</v>
+        <v>32.68679046630859</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>15.118577003479</v>
+        <v>17.23800277709961</v>
       </c>
       <c r="B38" t="n">
-        <v>15.58559322357178</v>
+        <v>13.5265417098999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>17.80952453613281</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="B39" t="n">
-        <v>9.793939590454102</v>
+        <v>19.2494068145752</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>24.50396919250488</v>
+        <v>13.2380952835083</v>
       </c>
       <c r="B40" t="n">
-        <v>28.82767868041992</v>
+        <v>18.09506607055664</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>8.952381134033203</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="B41" t="n">
-        <v>10.79373931884766</v>
+        <v>20.62446403503418</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>58.70000076293945</v>
+        <v>69.63761138916016</v>
       </c>
       <c r="B42" t="n">
-        <v>56.65620040893555</v>
+        <v>68.48290252685547</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>92.90000152587891</v>
+        <v>9.06403923034668</v>
       </c>
       <c r="B43" t="n">
-        <v>89.28058624267578</v>
+        <v>30.87078475952148</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8.380952835083008</v>
+        <v>12.54940700531006</v>
       </c>
       <c r="B44" t="n">
-        <v>26.29664039611816</v>
+        <v>13.03298091888428</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>18.31537628173828</v>
+        <v>24.70000076293945</v>
       </c>
       <c r="B45" t="n">
-        <v>10.22442626953125</v>
+        <v>13.77468204498291</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>68.5</v>
+        <v>10.91269874572754</v>
       </c>
       <c r="B46" t="n">
-        <v>60.35784149169922</v>
+        <v>15.79677200317383</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>70.80000305175781</v>
+        <v>34.70000076293945</v>
       </c>
       <c r="B47" t="n">
-        <v>64.70751953125</v>
+        <v>21.86193466186523</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>99.20635223388672</v>
+        <v>13.33333301544189</v>
       </c>
       <c r="B48" t="n">
-        <v>91.70586395263672</v>
+        <v>16.56705474853516</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2.644466161727905</v>
+        <v>13.5238094329834</v>
       </c>
       <c r="B49" t="n">
-        <v>11.17072105407715</v>
+        <v>14.65565395355225</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>40</v>
+        <v>14.22924900054932</v>
       </c>
       <c r="B50" t="n">
-        <v>52.34456253051758</v>
+        <v>20.49876594543457</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>60</v>
+        <v>13.32027435302734</v>
       </c>
       <c r="B51" t="n">
-        <v>57.43852233886719</v>
+        <v>17.67889022827148</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>99.20635223388672</v>
+        <v>14.19999980926514</v>
       </c>
       <c r="B52" t="n">
-        <v>92.81754302978516</v>
+        <v>32.49771118164062</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>25.95494651794434</v>
+        <v>29.39999961853027</v>
       </c>
       <c r="B53" t="n">
-        <v>25.15485382080078</v>
+        <v>35.19887161254883</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>22.60000038146973</v>
+        <v>17.29999923706055</v>
       </c>
       <c r="B54" t="n">
-        <v>18.69580268859863</v>
+        <v>17.04269981384277</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>97.94319152832031</v>
+        <v>22.9187068939209</v>
       </c>
       <c r="B55" t="n">
-        <v>104.6701965332031</v>
+        <v>16.54964637756348</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>23.11459350585938</v>
+        <v>21.13095283508301</v>
       </c>
       <c r="B56" t="n">
-        <v>24.13363075256348</v>
+        <v>16.07691383361816</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>5.320197105407715</v>
+        <v>11.43984222412109</v>
       </c>
       <c r="B57" t="n">
-        <v>13.2459135055542</v>
+        <v>14.43269157409668</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>13.80998992919922</v>
+        <v>30.55827713012695</v>
       </c>
       <c r="B58" t="n">
-        <v>10.55300331115723</v>
+        <v>17.33258819580078</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>24.5714282989502</v>
+        <v>22.6248779296875</v>
       </c>
       <c r="B59" t="n">
-        <v>18.18375396728516</v>
+        <v>8.577119827270508</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>68.85713958740234</v>
+        <v>22.5</v>
       </c>
       <c r="B60" t="n">
-        <v>63.08616256713867</v>
+        <v>10.7574291229248</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>69.90476226806641</v>
+        <v>29.60000038146973</v>
       </c>
       <c r="B61" t="n">
-        <v>64.05649566650391</v>
+        <v>25.16052055358887</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>9.027777671813965</v>
+        <v>26.09127044677734</v>
       </c>
       <c r="B62" t="n">
-        <v>8.082778930664062</v>
+        <v>16.23881530761719</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>141.6000061035156</v>
+        <v>30.15872955322266</v>
       </c>
       <c r="B63" t="n">
-        <v>135.8787994384766</v>
+        <v>12.74719429016113</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>39.17727661132812</v>
+        <v>27.79999923706055</v>
       </c>
       <c r="B64" t="n">
-        <v>40.53422546386719</v>
+        <v>7.836539268493652</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>17.53183174133301</v>
+        <v>26.40394020080566</v>
       </c>
       <c r="B65" t="n">
-        <v>13.69310283660889</v>
+        <v>9.598452568054199</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>34.09999847412109</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="B66" t="n">
-        <v>29.61758422851562</v>
+        <v>12.30843257904053</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>29.90476226806641</v>
+        <v>81</v>
       </c>
       <c r="B67" t="n">
-        <v>22.64069938659668</v>
+        <v>84.06996917724609</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>27.23809432983398</v>
+        <v>14.6245059967041</v>
       </c>
       <c r="B68" t="n">
-        <v>19.22282791137695</v>
+        <v>13.74543190002441</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>33.90000152587891</v>
+        <v>14.39764976501465</v>
       </c>
       <c r="B69" t="n">
-        <v>15.92141056060791</v>
+        <v>11.4104642868042</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>32.85714340209961</v>
+        <v>19.5</v>
       </c>
       <c r="B70" t="n">
-        <v>29.93810653686523</v>
+        <v>17.04520988464355</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>13.88888931274414</v>
+        <v>11.33333301544189</v>
       </c>
       <c r="B71" t="n">
-        <v>11.25662231445312</v>
+        <v>13.24766159057617</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>33.39862823486328</v>
+        <v>26.44466209411621</v>
       </c>
       <c r="B72" t="n">
-        <v>27.41666793823242</v>
+        <v>18.69206619262695</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>78.90000152587891</v>
+        <v>11.50793647766113</v>
       </c>
       <c r="B73" t="n">
-        <v>75.52748107910156</v>
+        <v>11.6872034072876</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>39.29999923706055</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="B74" t="n">
-        <v>34.65006637573242</v>
+        <v>68.93633270263672</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>69.73554992675781</v>
+        <v>22.51984214782715</v>
       </c>
       <c r="B75" t="n">
-        <v>68.6077880859375</v>
+        <v>24.44586372375488</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>8.227228164672852</v>
+        <v>20.27424049377441</v>
       </c>
       <c r="B76" t="n">
-        <v>13.676194190979</v>
+        <v>21.99702072143555</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>39.09999847412109</v>
+        <v>11.14285755157471</v>
       </c>
       <c r="B77" t="n">
-        <v>36.32306289672852</v>
+        <v>13.6548900604248</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>9.189723014831543</v>
+        <v>27.6785717010498</v>
       </c>
       <c r="B78" t="n">
-        <v>8.968734741210938</v>
+        <v>19.77636528015137</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>13.29365062713623</v>
+        <v>60</v>
       </c>
       <c r="B79" t="n">
-        <v>10.78231811523438</v>
+        <v>62.8114128112793</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>10.47430801391602</v>
+        <v>12.32741641998291</v>
       </c>
       <c r="B80" t="n">
-        <v>10.84660911560059</v>
+        <v>25.45219421386719</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>25.5238094329834</v>
+        <v>17.53183174133301</v>
       </c>
       <c r="B81" t="n">
-        <v>22.80103302001953</v>
+        <v>13.80677223205566</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>18.31537628173828</v>
+        <v>19.89999961853027</v>
       </c>
       <c r="B82" t="n">
-        <v>10.22442626953125</v>
+        <v>20.5562629699707</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>6.646825313568115</v>
+        <v>46.70000076293945</v>
       </c>
       <c r="B83" t="n">
-        <v>8.082103729248047</v>
+        <v>11.00748538970947</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>76.19047546386719</v>
+        <v>11.2380952835083</v>
       </c>
       <c r="B84" t="n">
-        <v>79.78961944580078</v>
+        <v>22.10980415344238</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>13.4285717010498</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B85" t="n">
-        <v>12.54451942443848</v>
+        <v>17.52926254272461</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>17.10000038146973</v>
+        <v>6.502462863922119</v>
       </c>
       <c r="B86" t="n">
-        <v>15.82324504852295</v>
+        <v>15.21539402008057</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>5.221674919128418</v>
+        <v>42.09999847412109</v>
       </c>
       <c r="B87" t="n">
-        <v>6.983545780181885</v>
+        <v>27.21880912780762</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>36.29999923706055</v>
+        <v>27.90476226806641</v>
       </c>
       <c r="B88" t="n">
-        <v>32.63071823120117</v>
+        <v>25.28923416137695</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>26.28968238830566</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="B89" t="n">
-        <v>25.08518028259277</v>
+        <v>20.03112030029297</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>20.53571510314941</v>
+        <v>37.59999847412109</v>
       </c>
       <c r="B90" t="n">
-        <v>21.20096588134766</v>
+        <v>31.97426986694336</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>6.646825313568115</v>
+        <v>10.34482765197754</v>
       </c>
       <c r="B91" t="n">
-        <v>8.082103729248047</v>
+        <v>10.18889141082764</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>21.23015785217285</v>
+        <v>70.80000305175781</v>
       </c>
       <c r="B92" t="n">
-        <v>25.99903297424316</v>
+        <v>65.46380615234375</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>59</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="B93" t="n">
-        <v>54.72017669677734</v>
+        <v>21.46257400512695</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>20.66601371765137</v>
+        <v>45</v>
       </c>
       <c r="B94" t="n">
-        <v>22.26672744750977</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>24.38785552978516</v>
-      </c>
-      <c r="B95" t="n">
-        <v>22.89851570129395</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>40.27777862548828</v>
-      </c>
-      <c r="B96" t="n">
-        <v>39.22438049316406</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>11.70634937286377</v>
-      </c>
-      <c r="B97" t="n">
-        <v>11.85715103149414</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>23.80952453613281</v>
-      </c>
-      <c r="B98" t="n">
-        <v>18.01867866516113</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>21.84133148193359</v>
-      </c>
-      <c r="B99" t="n">
-        <v>20.59012413024902</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>18</v>
-      </c>
-      <c r="B100" t="n">
-        <v>22.19892692565918</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>17.94871711730957</v>
-      </c>
-      <c r="B101" t="n">
-        <v>19.05369186401367</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>5.320197105407715</v>
-      </c>
-      <c r="B102" t="n">
-        <v>13.2459135055542</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>129.3000030517578</v>
-      </c>
-      <c r="B103" t="n">
-        <v>140.4494934082031</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>5.582761764526367</v>
-      </c>
-      <c r="B104" t="n">
-        <v>10.21337604522705</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>24.87757110595703</v>
-      </c>
-      <c r="B105" t="n">
-        <v>22.98507881164551</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>26.40394020080566</v>
-      </c>
-      <c r="B106" t="n">
-        <v>17.00259780883789</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>8.952381134033203</v>
-      </c>
-      <c r="B107" t="n">
-        <v>10.79373931884766</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>20.47012710571289</v>
-      </c>
-      <c r="B108" t="n">
-        <v>19.92120933532715</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>19.84127044677734</v>
-      </c>
-      <c r="B109" t="n">
-        <v>14.84048080444336</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>24.50396919250488</v>
-      </c>
-      <c r="B110" t="n">
-        <v>28.82767868041992</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>10.91269874572754</v>
-      </c>
-      <c r="B111" t="n">
-        <v>12.93724536895752</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>39.68254089355469</v>
-      </c>
-      <c r="B112" t="n">
-        <v>39.56050109863281</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>1.665034294128418</v>
-      </c>
-      <c r="B113" t="n">
-        <v>5.809543609619141</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="B114" t="n">
-        <v>25.16118621826172</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>13.32027435302734</v>
-      </c>
-      <c r="B115" t="n">
-        <v>13.00931644439697</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>14.19999980926514</v>
-      </c>
-      <c r="B116" t="n">
-        <v>18.85551834106445</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>29.39999961853027</v>
-      </c>
-      <c r="B117" t="n">
-        <v>31.86118125915527</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>58.76591491699219</v>
-      </c>
-      <c r="B118" t="n">
-        <v>65.18425750732422</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>19.58863830566406</v>
-      </c>
-      <c r="B119" t="n">
-        <v>30.31307792663574</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>10.34482765197754</v>
-      </c>
-      <c r="B120" t="n">
-        <v>9.031352043151855</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>26.09127044677734</v>
-      </c>
-      <c r="B121" t="n">
-        <v>17.52283096313477</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>40.47618865966797</v>
-      </c>
-      <c r="B122" t="n">
-        <v>37.37861633300781</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>30.15872955322266</v>
-      </c>
-      <c r="B123" t="n">
-        <v>20.73200225830078</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>81</v>
-      </c>
-      <c r="B124" t="n">
-        <v>72.83824920654297</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>44.70000076293945</v>
-      </c>
-      <c r="B125" t="n">
-        <v>41.71706008911133</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="B126" t="n">
-        <v>14.51790237426758</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>26.44466209411621</v>
-      </c>
-      <c r="B127" t="n">
-        <v>26.46675682067871</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>11.50793647766113</v>
-      </c>
-      <c r="B128" t="n">
-        <v>11.08079242706299</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>22.51984214782715</v>
-      </c>
-      <c r="B129" t="n">
-        <v>25.37757110595703</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>20.27424049377441</v>
-      </c>
-      <c r="B130" t="n">
-        <v>21.51331901550293</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>27.81586647033691</v>
-      </c>
-      <c r="B131" t="n">
-        <v>27.85268020629883</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>38.39373016357422</v>
-      </c>
-      <c r="B132" t="n">
-        <v>44.64463424682617</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>27.6785717010498</v>
-      </c>
-      <c r="B133" t="n">
-        <v>26.67249870300293</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>60</v>
-      </c>
-      <c r="B134" t="n">
-        <v>66.32160949707031</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>12.32741641998291</v>
-      </c>
-      <c r="B135" t="n">
-        <v>14.40518283843994</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>60</v>
-      </c>
-      <c r="B136" t="n">
-        <v>59.44004821777344</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>46.70000076293945</v>
-      </c>
-      <c r="B137" t="n">
-        <v>34.97585296630859</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>6.94444465637207</v>
-      </c>
-      <c r="B138" t="n">
-        <v>6.645462989807129</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>6.502462863922119</v>
-      </c>
-      <c r="B139" t="n">
-        <v>5.536012172698975</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>34.37805938720703</v>
-      </c>
-      <c r="B140" t="n">
-        <v>24.55009269714355</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>27.90476226806641</v>
-      </c>
-      <c r="B141" t="n">
-        <v>25.69201469421387</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>13.10000038146973</v>
-      </c>
-      <c r="B142" t="n">
-        <v>14.66553401947021</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>79.36508178710938</v>
-      </c>
-      <c r="B143" t="n">
-        <v>72.87423706054688</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>70.80000305175781</v>
-      </c>
-      <c r="B144" t="n">
-        <v>64.70751953125</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>18.70000076293945</v>
-      </c>
-      <c r="B145" t="n">
-        <v>19.62419509887695</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="B146" t="n">
-        <v>31.1666316986084</v>
+        <v>51.96989059448242</v>
       </c>
     </row>
   </sheetData>
